--- a/stories/arbres/TREE-EMO-019.xlsx
+++ b/stories/arbres/TREE-EMO-019.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Inès marche vers l'école avec maman. Un cartable glisse. Inès a les joues chaudes. Elle est en colère. Ce n'est pas une honte. Les mains restent loin. Inès s'éloigne. Elle va vers maman, l'adulte. Papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1509,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1538,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Inès arrive près du bac à sable. Une feuille tombe. Quelque chose ne va pas. Inès dit : je suis en colère. Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
+          <t>Inès arrive près du bac à sable. Une feuille tombe. Quelque chose ne va pas. Je suis en colère. Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1676,13 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Inès arrive près du bac à sable. Une feuille tombe. Quelque chose ne va pas.
+enfant-f|Je suis en colère.
+narrateur|Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a les poings chauds. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Colère. Mains loin. Inès s'éloigne. Vers l'adulte. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le ballon rouge. Un petit bruit d'eau. Les mains restent loin du ballon rouge. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2555,7 +2614,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. On entend un oiseau. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. On entend un oiseau. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2693,6 +2752,13 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. On entend un oiseau. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2921,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2879,7 +2950,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Ça sent l'herbe coupée. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Ça sent l'herbe coupée. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3017,6 +3088,13 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Ça sent l'herbe coupée. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3257,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3203,7 +3286,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3341,6 +3424,13 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3593,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3760,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le seau bleu. Les chaussures font toc toc. Les mains restent loin du seau bleu. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3955,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3879,7 +3984,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. Ça sent l'herbe coupée. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. Ça sent l'herbe coupée. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4017,6 +4122,13 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. Ça sent l'herbe coupée. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4291,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4203,7 +4320,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4341,6 +4458,13 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4627,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4656,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Le sol est frais. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Le sol est frais. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4794,13 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Le sol est frais. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4963,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4989,6 +5130,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le doudou. Un vélo passe au loin. Les mains restent loin du doudou. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5179,6 +5325,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5203,7 +5354,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5341,6 +5492,13 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5503,6 +5661,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5527,7 +5690,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Le sol est frais. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Le sol est frais. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5665,6 +5828,13 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Le sol est frais. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5827,6 +5997,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5851,7 +6026,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Un petit bruit d'eau. Près du bac à sable, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Un petit bruit d'eau. Près du bac à sable, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -5989,6 +6164,13 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Un petit bruit d'eau. Près du bac à sable, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6151,6 +6333,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6175,7 +6362,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Inès arrive près du toboggan. Le vent est doux. Quelque chose ne va pas. Inès dit : je suis en colère. Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
+          <t>Inès arrive près du toboggan. Le vent est doux. Quelque chose ne va pas. Je suis en colère. Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6313,6 +6500,13 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Inès arrive près du toboggan. Le vent est doux. Quelque chose ne va pas.
+enfant-f|Je suis en colère.
+narrateur|Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6489,6 +6683,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a les poings chauds. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -6657,6 +6856,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Colère. Mains loin. Inès s'éloigne. Vers l'adulte. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7047,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7005,6 +7214,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le ballon rouge. Un petit bruit d'eau. Les mains restent loin du ballon rouge. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7195,6 +7409,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7219,7 +7438,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. Ça sent l'herbe coupée. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. Ça sent l'herbe coupée. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7357,6 +7576,13 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. Ça sent l'herbe coupée. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7519,6 +7745,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7543,7 +7774,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Le soleil chauffe un peu. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Le soleil chauffe un peu. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7681,6 +7912,13 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Le soleil chauffe un peu. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7843,6 +8081,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7867,7 +8110,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Le sol est frais. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Le sol est frais. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8005,6 +8248,13 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Le sol est frais. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8167,6 +8417,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8329,6 +8584,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le seau bleu. Les chaussures font toc toc. Les mains restent loin du seau bleu. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8519,6 +8779,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8543,7 +8808,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8681,6 +8946,13 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8843,6 +9115,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8867,7 +9144,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Le sol est frais. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Le sol est frais. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9005,6 +9282,13 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Le sol est frais. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9167,6 +9451,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9191,7 +9480,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Un petit bruit d'eau. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Un petit bruit d'eau. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9329,6 +9618,13 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Un petit bruit d'eau. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9491,6 +9787,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9653,6 +9954,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le doudou. Un vélo passe au loin. Les mains restent loin du doudou. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9843,6 +10149,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9867,7 +10178,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. Le sol est frais. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. Le sol est frais. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10005,6 +10316,13 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. Le sol est frais. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10167,6 +10485,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10191,7 +10514,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Un petit bruit d'eau. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Un petit bruit d'eau. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10329,6 +10652,13 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Un petit bruit d'eau. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10491,6 +10821,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10515,7 +10850,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Les chaussures font toc toc. Près du toboggan, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Les chaussures font toc toc. Près du toboggan, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10653,6 +10988,13 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Les chaussures font toc toc. Près du toboggan, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10815,6 +11157,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10839,7 +11186,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Inès arrive près des balançoires. On entend un oiseau. Quelque chose ne va pas. Inès dit : je suis en colère. Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
+          <t>Inès arrive près des balançoires. On entend un oiseau. Quelque chose ne va pas. Je suis en colère. Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10977,6 +11324,13 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Inès arrive près des balançoires. On entend un oiseau. Quelque chose ne va pas.
+enfant-f|Je suis en colère.
+narrateur|Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11153,6 +11507,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Inès a les poings chauds. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -11321,6 +11680,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Colère. Mains loin. Inès s'éloigne. Vers l'adulte. On continue avec maman.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11507,6 +11871,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11669,6 +12038,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le ballon rouge. Un petit bruit d'eau. Les mains restent loin du ballon rouge. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11859,6 +12233,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11883,7 +12262,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12021,6 +12400,13 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. Le soleil chauffe un peu. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12183,6 +12569,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12207,7 +12598,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Le sol est frais. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Le sol est frais. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12345,6 +12736,13 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Le sol est frais. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12507,6 +12905,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12531,7 +12934,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Un petit bruit d'eau. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Un petit bruit d'eau. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -12669,6 +13072,13 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Un petit bruit d'eau. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12831,6 +13241,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12993,6 +13408,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le seau bleu. Les chaussures font toc toc. Les mains restent loin du seau bleu. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13183,6 +13603,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13207,7 +13632,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. Le sol est frais. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. Le sol est frais. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13345,6 +13770,13 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. Le sol est frais. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13507,6 +13939,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13531,7 +13968,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Un petit bruit d'eau. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Un petit bruit d'eau. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -13669,6 +14106,13 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Un petit bruit d'eau. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13831,6 +14275,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13855,7 +14304,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Les chaussures font toc toc. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Les chaussures font toc toc. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13993,6 +14442,13 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Les chaussures font toc toc. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14155,6 +14611,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14317,6 +14778,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Inès pose le doudou. Un vélo passe au loin. Les mains restent loin du doudou. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14507,6 +14973,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14531,7 +15002,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Tom après la pause. Un petit bruit d'eau. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Tom après la pause. Un petit bruit d'eau. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -14669,6 +15140,13 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Tom après la pause. Un petit bruit d'eau. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14831,6 +15309,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14855,7 +15338,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Léa après la pause. Les chaussures font toc toc. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Léa après la pause. Les chaussures font toc toc. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -14993,6 +15476,13 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Léa après la pause. Les chaussures font toc toc. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15155,6 +15645,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15179,7 +15674,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Inès rejoint Sami après la pause. Un vélo passe au loin. Près des balançoires, Inès a dit : je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+          <t>Inès rejoint Sami après la pause. Un vélo passe au loin. Près des balançoires, Inès Je suis en colère. Mains loin. Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15317,6 +15812,13 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Inès rejoint Sami après la pause. Un vélo passe au loin. Près des balançoires, Inès
+enfant-f|Je suis en colère. Mains loin.
+narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15479,6 +15981,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15497,7 +16004,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15570,6 +16077,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-EMO-019.xlsx
+++ b/stories/arbres/TREE-EMO-019.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Inès marche vers l'école avec maman. Un cartable glisse. Inès a les joues chaudes. Elle est en colère. Ce n'est pas une honte. Les mains restent loin. Inès s'éloigne. Elle va vers maman, l'adulte. Papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1520,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
 narrateur|Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|Inès a les poings chauds. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Oui. Colère. Mains loin. Inès s'éloigne. Vers l'adulte. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Inès pose le ballon rouge. Un petit bruit d'eau. Les mains restent loin du ballon rouge. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2759,6 +2772,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2926,6 +2940,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3095,6 +3110,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3262,6 +3278,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3448,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3765,6 +3784,7 @@
           <t>narrateur|Inès pose le seau bleu. Les chaussures font toc toc. Les mains restent loin du seau bleu. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3960,6 +3980,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4129,6 +4150,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4296,6 +4318,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4465,6 +4488,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4632,6 +4656,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4801,6 +4826,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4968,6 +4994,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5135,6 +5162,7 @@
           <t>narrateur|Inès pose le doudou. Un vélo passe au loin. Les mains restent loin du doudou. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5330,6 +5358,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5499,6 +5528,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5666,6 +5696,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5835,6 +5866,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -6002,6 +6034,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6171,6 +6204,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6338,6 +6372,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6507,6 +6542,7 @@
 narrateur|Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6690,6 +6726,7 @@
           <t>narrateur|Inès a les poings chauds. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6861,6 +6898,7 @@
           <t>narrateur|Oui. Colère. Mains loin. Inès s'éloigne. Vers l'adulte. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7052,6 +7090,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7219,6 +7258,7 @@
           <t>narrateur|Inès pose le ballon rouge. Un petit bruit d'eau. Les mains restent loin du ballon rouge. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7414,6 +7454,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7583,6 +7624,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7750,6 +7792,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7919,6 +7962,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8086,6 +8130,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8255,6 +8300,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8422,6 +8468,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8589,6 +8636,7 @@
           <t>narrateur|Inès pose le seau bleu. Les chaussures font toc toc. Les mains restent loin du seau bleu. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8784,6 +8832,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8953,6 +9002,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9120,6 +9170,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9289,6 +9340,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9456,6 +9508,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9625,6 +9678,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9792,6 +9846,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9959,6 +10014,7 @@
           <t>narrateur|Inès pose le doudou. Un vélo passe au loin. Les mains restent loin du doudou. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10154,6 +10210,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10323,6 +10380,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10490,6 +10548,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10659,6 +10718,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10826,6 +10886,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10995,6 +11056,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11162,6 +11224,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11331,6 +11394,7 @@
 narrateur|Les mains restent loin. Inès s'éloigne. Vers maman, l'adulte.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11514,6 +11578,7 @@
           <t>narrateur|Inès a les poings chauds. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11685,6 +11750,7 @@
           <t>narrateur|Oui. Colère. Mains loin. Inès s'éloigne. Vers l'adulte. On continue avec maman.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11876,6 +11942,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12043,6 +12110,7 @@
           <t>narrateur|Inès pose le ballon rouge. Un petit bruit d'eau. Les mains restent loin du ballon rouge. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12238,6 +12306,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12407,6 +12476,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12574,6 +12644,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12743,6 +12814,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12910,6 +12982,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13079,6 +13152,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13246,6 +13320,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13413,6 +13488,7 @@
           <t>narrateur|Inès pose le seau bleu. Les chaussures font toc toc. Les mains restent loin du seau bleu. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13608,6 +13684,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13777,6 +13854,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13944,6 +14022,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14113,6 +14192,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14280,6 +14360,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14449,6 +14530,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14616,6 +14698,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14783,6 +14866,7 @@
           <t>narrateur|Inès pose le doudou. Un vélo passe au loin. Les mains restent loin du doudou. Inès est en colère. Inès s'éloigne. Vers maman, l'adulte. papa n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14978,6 +15062,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15147,6 +15232,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15314,6 +15400,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15483,6 +15570,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15650,6 +15738,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15819,6 +15908,7 @@
 narrateur|Inès s'est éloignée. Vers maman, l'adulte. Merci maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15986,6 +16076,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16004,7 +16095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16084,6 +16175,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16098,7 +16203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16285,6 +16390,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
